--- a/docs/AlloQuant_output_file_manifest_v7r3.xlsx
+++ b/docs/AlloQuant_output_file_manifest_v7r3.xlsx
@@ -510,14 +510,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Reference run: CSK-SRC dimer scan, 260718 rerun (AF3-complete)   |   generated 2026-07-30</t>
+          <t>Reference run: CSK-SRC dimer scan, 260718 rerun (AF3-complete)   |   generated 2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>- AlloQuant is a two-module pipeline. Module 1 (structural extraction) writes the run-root files below; Module 2 (allostery discovery) writes one plots_and_stats_{KINASE}_{METHOD}/ folder per analysed kinase.</t>
+          <t>- AlloQuant is a two-module pipeline. Module 1 (structural extraction) writes the run-root files below, except row 1: experiment.csv is the user-supplied design file it reads. Module 2 (allostery discovery) writes one plots_and_stats_{KINASE}_{METHOD}/ folder per analysed kinase.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -607,7 +606,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>User input</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -627,7 +626,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Experiment design table: one row per dimer condition (chain_a, condition_a, chain_b, ptm_b, condition_b). Defines the systems built and analysed.</t>
+          <t>User-supplied experimental design metadata: one row per dimer condition (chain_a, condition_a, chain_b, ptm_b, condition_b). Read by the pipeline to define the systems built and analysed; it is not written by AlloQuant and is excluded from run archiving.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
